--- a/calibration-devices.xlsx
+++ b/calibration-devices.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Outros computadores\O meu portátil\DOUTORADO\UMRAE\PAPER2\smarthphone_sound_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D257B1A7-EDDD-4A50-86A6-CF4A9CC775A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10860346-5F05-4EBE-9E1C-BB1499F0E098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="mobile_sensors" sheetId="1" r:id="rId1"/>
+    <sheet name="fix_sensors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>device</t>
   </si>
@@ -95,9 +96,6 @@
     <t>Galaxy S21 FE</t>
   </si>
   <si>
-    <t>advanced</t>
-  </si>
-  <si>
     <t>Galaxy A55</t>
   </si>
   <si>
@@ -108,12 +106,43 @@
   </si>
   <si>
     <t>gain_calibration</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>fixsensor</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>referenceiphone</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>android_advanced</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000000000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -133,12 +162,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -146,6 +169,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,23 +199,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,7 +509,7 @@
     <col min="1" max="1" width="14.21875" customWidth="1"/>
     <col min="2" max="3" width="18.21875" customWidth="1"/>
     <col min="4" max="4" width="24.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,97 +526,162 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>23</v>
+      <c r="F1" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="4" t="str">
         <f t="shared" ref="D2:D3" si="0">C2</f>
         <v>Iphone</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="4" t="str">
         <f t="shared" si="0"/>
         <v>Iphone</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22E1EB7-2EE8-47FD-B8AC-C683C60100F2}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="7">
+        <v>-46.729826000000003</v>
+      </c>
+      <c r="D2" s="7">
+        <v>-23.560203999999999</v>
+      </c>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8">
+        <v>-46.730371748078802</v>
+      </c>
+      <c r="D3" s="7">
+        <v>-23.560375000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="8"/>
+      <c r="D4" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>